--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488000_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488000_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. GONZALEZ NAVARRETE</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2467</v>
+        <v>1.5572</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0624</v>
+        <v>3.7865</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3091</v>
+        <v>-2.2293</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4075</v>
+        <v>-1.5256</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4075</v>
+        <v>-0.9031</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.4308</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.3707</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.0602</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4075</v>
+        <v>-2.9565</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0.9932</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4075</v>
+        <v>-1.9633</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1608</v>
+        <v>0.4881</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0624</v>
+        <v>0.1396</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0984</v>
+        <v>0.3485</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>L. GONZALEZ NAVARRETE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2306</v>
+        <v>0.3029</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9091</v>
+        <v>-0.0624</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.6785</v>
+        <v>0.3652</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5256</v>
+        <v>0.4075</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9031</v>
+        <v>0.4075</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4308</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3707</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0602</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9565</v>
+        <v>0.4075</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9932</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9633</v>
+        <v>0.4075</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8385</v>
+        <v>-0.1046</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7377</v>
+        <v>-0.0624</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1007</v>
+        <v>-0.0422</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.844</v>
+        <v>-0.907</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6922</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5362</v>
+        <v>-0.8419</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2766</v>
+        <v>-0.7795</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.253</v>
+        <v>-0.3834</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0236</v>
+        <v>-0.3961</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209</v>
+        <v>0.0202</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3975</v>
+        <v>-0.7996</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3337</v>
+        <v>-0.4036</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0638</v>
+        <v>-0.3961</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2625</v>
+        <v>-0.1276</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3047</v>
+        <v>-0.0853</v>
       </c>
       <c r="U4" t="n">
         <v>-0.0422</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0282</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.065</v>
+        <v>-0.9074</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.167</v>
+        <v>0.4885</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.898</v>
+        <v>-1.3958</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7795</v>
+        <v>-1.2766</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3834</v>
+        <v>-0.253</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3961</v>
+        <v>-1.0236</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0202</v>
+        <v>0.1209</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0202</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7996</v>
+        <v>-1.3975</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4036</v>
+        <v>-0.3337</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3961</v>
+        <v>-1.0638</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2856</v>
+        <v>0.1992</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1872</v>
+        <v>0.101</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0984</v>
+        <v>0.0982</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.0282</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2641</v>
+        <v>-1.7601</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6635</v>
+        <v>-0.038</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9276</v>
+        <v>-1.7221</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.271</v>
+        <v>-2.923</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0015</v>
+        <v>0.343</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2725</v>
+        <v>-3.2661</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6427</v>
+        <v>0.771</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3972</v>
+        <v>1.4061</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2455</v>
+        <v>-0.6351</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9137</v>
+        <v>-3.6941</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3957</v>
+        <v>-1.0631</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.518</v>
+        <v>-2.631</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5947</v>
+        <v>0.5947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8368</v>
+        <v>0.5965</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7453</v>
+        <v>0.4507</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0915</v>
+        <v>0.1457</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2353</v>
+        <v>-0.0282</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>-0.0704</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5018</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6943</v>
+        <v>-2.1208</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.398</v>
+        <v>1.256</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2964</v>
+        <v>-3.3768</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9721</v>
+        <v>-1.271</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0517</v>
+        <v>0.0015</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9205</v>
+        <v>-1.2725</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2018</v>
+        <v>1.6427</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3223</v>
+        <v>0.3972</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>1.2455</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7704</v>
+        <v>-2.9137</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7294</v>
+        <v>-0.3957</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.041</v>
+        <v>-2.518</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.7662</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.1538</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3038</v>
+        <v>0.9801</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2173</v>
+        <v>0.3378</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.6422</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7403</v>
+        <v>-1.2353</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. KOROL</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9798</v>
+        <v>-2.1709</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9127999999999999</v>
+        <v>-1.7326</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8927</v>
+        <v>-0.4383</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3303</v>
+        <v>-1.0752</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6467</v>
+        <v>-0.6791</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.977</v>
+        <v>-0.3961</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6365</v>
+        <v>-0.6791</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2314</v>
+        <v>-0.6791</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5949</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9668</v>
+        <v>-0.3961</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4153</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3822</v>
+        <v>-0.3961</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3281</v>
+        <v>-0.1046</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9325</v>
+        <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3956</v>
+        <v>-0.0422</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1758</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>N. KOROL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1782</v>
+        <v>-2.1773</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7483</v>
+        <v>0.7715</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4299</v>
+        <v>-2.9488</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9193</v>
+        <v>-1.3303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.312</v>
+        <v>1.6467</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.2313</v>
+        <v>-2.977</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.062</v>
+        <v>0.6365</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6546</v>
+        <v>1.2314</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.7165</v>
+        <v>-0.5949</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8574</v>
+        <v>-1.9668</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3426</v>
+        <v>0.4153</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5148</v>
+        <v>-2.3822</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1375</v>
+        <v>1.1306</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3047</v>
+        <v>0.7912</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8328</v>
+        <v>0.3394</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.1758</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.7089</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2271</v>
+        <v>-2.7927</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7326</v>
+        <v>-2.0539</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4945</v>
+        <v>-0.7388</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0752</v>
+        <v>-2.9193</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6791</v>
+        <v>0.312</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3961</v>
+        <v>-3.2313</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6791</v>
+        <v>-1.062</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6791</v>
+        <v>1.6546</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.7165</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3961</v>
+        <v>-1.8574</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.3426</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3961</v>
+        <v>-0.5148</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1608</v>
+        <v>0.5231</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0624</v>
+        <v>-0.0009</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0984</v>
+        <v>0.5239</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0338</v>
+        <v>-3.2723</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6097</v>
+        <v>-2.8636</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.424</v>
+        <v>-0.4087</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.923</v>
+        <v>-1.9721</v>
       </c>
       <c r="H11" t="n">
-        <v>0.343</v>
+        <v>-1.0517</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2661</v>
+        <v>-0.9205</v>
       </c>
       <c r="J11" t="n">
-        <v>0.771</v>
+        <v>-0.2018</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4061</v>
+        <v>-0.3223</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6351</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6941</v>
+        <v>-1.7704</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0631</v>
+        <v>-0.7294</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.631</v>
+        <v>-1.041</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5947</v>
+        <v>-3.7662</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1893</v>
+        <v>-5.1538</v>
       </c>
       <c r="R11" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6772</v>
+        <v>0.7258</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.121</v>
+        <v>0.7517</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5562</v>
+        <v>-0.0259</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0282</v>
+        <v>1.7403</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0704</v>
+        <v>1.7403</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6483</v>
+        <v>-4.8199</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3954</v>
+        <v>-1.3143</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2529</v>
+        <v>-3.5056</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5192</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6941000000000001</v>
+        <v>1.5224</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4881</v>
+        <v>0.5929</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1822</v>
+        <v>0.9295</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8498</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.2279</v>
+        <v>-8.305</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2114</v>
+        <v>-6.0077</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0165</v>
+        <v>-2.2973</v>
       </c>
       <c r="G13" t="n">
         <v>-2.491</v>
@@ -1468,13 +1468,13 @@
         <v>0.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0293</v>
+        <v>-0.0477</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.624</v>
+        <v>-0.4202</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6533</v>
+        <v>0.3725</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.6852</v>
+        <v>-27.3733</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.1472</v>
+        <v>-7.835099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.5381</v>
+        <v>-19.5382</v>
       </c>
       <c r="G14" t="n">
         <v>-17.6753</v>
@@ -1519,7 +1519,7 @@
         <v>-17.966</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4435</v>
+        <v>4.443499999999999</v>
       </c>
       <c r="K14" t="n">
         <v>7.2744</v>
@@ -1546,19 +1546,19 @@
         <v>8.92</v>
       </c>
       <c r="S14" t="n">
-        <v>5.4692</v>
+        <v>5.7813</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2217</v>
+        <v>2.5337</v>
       </c>
       <c r="U14" t="n">
-        <v>3.247599999999999</v>
+        <v>3.2474</v>
       </c>
       <c r="V14" t="n">
         <v>-4.577</v>
       </c>
       <c r="W14" t="n">
-        <v>5.009600000000001</v>
+        <v>5.0096</v>
       </c>
       <c r="X14" t="n">
         <v>-9.586300000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>12.7983</v>
+        <v>11.295</v>
       </c>
       <c r="E15" t="n">
-        <v>9.633699999999999</v>
+        <v>8.411199999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1646</v>
+        <v>2.8838</v>
       </c>
       <c r="G15" t="n">
         <v>8.310600000000001</v>
@@ -1624,13 +1624,13 @@
         <v>3.568</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3069</v>
+        <v>-0.1963</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0942</v>
+        <v>-0.1282</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2127</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3873</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10.3663</v>
+        <v>10.2083</v>
       </c>
       <c r="E16" t="n">
-        <v>8.0008</v>
+        <v>7.899</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3655</v>
+        <v>2.3093</v>
       </c>
       <c r="G16" t="n">
         <v>6.6112</v>
@@ -1702,13 +1702,13 @@
         <v>3.3698</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0667</v>
+        <v>-0.2248</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0145</v>
+        <v>-0.1163</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0523</v>
+        <v>-0.1084</v>
       </c>
       <c r="V16" t="n">
         <v>2.4343</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6069</v>
+        <v>6.1959</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7769</v>
+        <v>4.2862</v>
       </c>
       <c r="F17" t="n">
-        <v>1.83</v>
+        <v>1.9097</v>
       </c>
       <c r="G17" t="n">
         <v>3.6136</v>
@@ -1780,13 +1780,13 @@
         <v>2.5769</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4984</v>
+        <v>-0.9094</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3727</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1257</v>
+        <v>-0.046</v>
       </c>
       <c r="V17" t="n">
         <v>2.8971</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2593</v>
+        <v>1.2756</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4816</v>
+        <v>-1.6853</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7409</v>
+        <v>2.9609</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5322</v>
@@ -1858,13 +1858,13 @@
         <v>3.568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3475</v>
+        <v>-0.3312</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0769</v>
+        <v>-0.2806</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2707</v>
+        <v>-0.0506</v>
       </c>
       <c r="V18" t="n">
         <v>0.5532</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. PAÑOS HUERTAS</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9053</v>
+        <v>1.0872</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9053</v>
+        <v>0.1534</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.9339</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9053</v>
+        <v>2.4137</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3027</v>
+        <v>1.501</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6027</v>
+        <v>0.9127</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9053</v>
+        <v>2.4429</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3027</v>
+        <v>2.2265</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6027</v>
+        <v>0.2164</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.0292</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.7255</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.6962</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.1716</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-1.4545</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.8405</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.6141</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.0612</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>L. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4036</v>
+        <v>0.9053</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2541</v>
+        <v>0.9053</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6577</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4137</v>
+        <v>0.9053</v>
       </c>
       <c r="H20" t="n">
-        <v>1.501</v>
+        <v>0.3027</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9127</v>
+        <v>0.6027</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4429</v>
+        <v>0.9053</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2265</v>
+        <v>0.3027</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2164</v>
+        <v>0.6027</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0292</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7255</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6962</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1716</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1382</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2479</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8903</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0612</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0333</v>
+        <v>0.1352</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9936</v>
+        <v>1.0955</v>
       </c>
       <c r="F21" t="n">
         <v>-0.9603</v>
@@ -2092,10 +2092,10 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.334</v>
+        <v>-0.2322</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U21" t="n">
         <v>0.0403</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4512</v>
+        <v>-0.3212</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3528</v>
+        <v>0.3808</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5433</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1061</v>
+        <v>0.0239</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-0.4208</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1639</v>
+        <v>1.5427</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2714</v>
+        <v>-1.9635</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1782</v>
+        <v>-0.4498</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2274</v>
+        <v>-0.2815</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9508</v>
+        <v>-0.1682</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9144</v>
+        <v>0.5866</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4439</v>
+        <v>0.3701</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3583</v>
+        <v>0.2164</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2638</v>
+        <v>-1.0363</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6713</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4075</v>
+        <v>-0.3847</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3964</v>
+        <v>2.1805</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1109</v>
+        <v>-0.8938</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2496</v>
+        <v>-0.4669</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1387</v>
+        <v>-0.4269</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9112</v>
+        <v>-0.745</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4408</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3521</v>
+        <v>0.2152</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4498</v>
+        <v>-1.1782</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2815</v>
+        <v>-0.2274</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1682</v>
+        <v>-0.9508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5866</v>
+        <v>-0.9144</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3701</v>
+        <v>0.4439</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2164</v>
+        <v>-1.3583</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0363</v>
+        <v>-0.2638</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6713</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3847</v>
+        <v>0.4075</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1805</v>
+        <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3842</v>
+        <v>0.0367</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5688</v>
+        <v>-0.0459</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8154</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.6808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4326</v>
+        <v>-1.251</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5095</v>
+        <v>-1.4077</v>
       </c>
       <c r="F25" t="n">
-        <v>0.077</v>
+        <v>0.1566</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2482</v>
@@ -2404,13 +2404,13 @@
         <v>0.1982</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.79</v>
+        <v>-0.6085</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.478</v>
+        <v>-0.3983</v>
       </c>
       <c r="V25" t="n">
         <v>0.4074</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>27.68539999999999</v>
+        <v>28.3645</v>
       </c>
       <c r="E26" t="n">
-        <v>19.5381</v>
+        <v>19.538</v>
       </c>
       <c r="F26" t="n">
-        <v>8.147499999999999</v>
+        <v>8.826399999999998</v>
       </c>
       <c r="G26" t="n">
         <v>17.6754</v>
@@ -2482,13 +2482,13 @@
         <v>19.8223</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.4691</v>
+        <v>-4.7901</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.2474</v>
+        <v>-3.2473</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.222</v>
+        <v>-1.5427</v>
       </c>
       <c r="V26" t="n">
         <v>4.576899999999999</v>
